--- a/review/data/workbooks/Updated Safeguarding 2026.xlsx
+++ b/review/data/workbooks/Updated Safeguarding 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lcnow-my.sharepoint.com/personal/elestoneham_lcnow_onmicrosoft_com/Documents/Leadership Capacity Now LCN/Oxlip/Oxlip/School Improvement/Framework for SI/OSED/new OSED/Supporting Tools/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lcnow-my.sharepoint.com/personal/elestoneham_lcnow_onmicrosoft_com/Documents/Leadership Capacity Now LCN/Oxlip/Oxlip/School Improvement/Framework for SI/OSED/new OSED/Supporting Tools/Sent to Phil and uploaded on hub/Round 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="385" documentId="8_{5233234A-F291-D14C-AC43-5709A59352BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AAB55E8-01E6-41A7-BE8A-E05295458481}"/>
+  <xr:revisionPtr revIDLastSave="391" documentId="8_{5233234A-F291-D14C-AC43-5709A59352BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4888129-C62A-4EF4-A27D-EDC9E81689CB}"/>
   <bookViews>
-    <workbookView xWindow="31620" yWindow="1740" windowWidth="23550" windowHeight="13440" xr2:uid="{6C280336-9442-5945-A54D-D346D2364797}"/>
+    <workbookView xWindow="29580" yWindow="870" windowWidth="23550" windowHeight="13440" xr2:uid="{6C280336-9442-5945-A54D-D346D2364797}"/>
   </bookViews>
   <sheets>
     <sheet name="Met" sheetId="1" r:id="rId1"/>
@@ -171,15 +171,6 @@
     <t>The quality of care in nursery provision (where applicable) is such that children have been harmed or are at risk of harm</t>
   </si>
   <si>
-    <t>Can you see this across the school? Is safeguarding clearly understood as everyone’s responsibility across the school? Can leaders demonstrate strong oversight of safeguarding practice, including how they review and act on concerns? How effective is multi-agency working in securing support for pupils and families (and how effectively is it evidenced and seen in chronology recording that suitable suppotr has been sought at each stage and the needs of children and families championed)? Is there a culture of reveiw and learning lessons to continually improve practice?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do pupils say they feel safe, and can they identify trusted adults to go to? What does pupil voice indicate about how well concerns are listened to and acted upon and their confidence in who to go to if they need support? Is safeguarding, including online safety, embedded in what pupils are taught? How do leaders ensure that pupils off-site are safe and accounted for? </t>
-  </si>
-  <si>
-    <t>Do staff understand the signs of safeguarding concerns and know how to report them? Does training meet statutory requirements?  Are safeguarding systems used consistently in practice? Can leaders demonstrate that concerns are recorded, followed up and escalated appropriately? How do leaders assure themselves that staff responses are timely and effective?</t>
-  </si>
-  <si>
     <t>Are incidents of child-on-child abuse identified, recorded and addressed effectively? Is there clear evidence of appropriate support for both victims and those responsible? As a school, has this been addressed both with staff and with students?</t>
   </si>
   <si>
@@ -284,6 +275,15 @@
   </si>
   <si>
     <t>To strengthen this area, we will improve sixth-form students' understanding of the full range of safeguarding, wellbeing and external support available to them. We will review how safeguarding information is communicated through tutorials, enrichment activities and transition events and ensure that support pathways are revisited throughout Years 12 and 13 rather than solely during induction. We will gather pupil voice more frequently from sixth-form students to evaluate the impact of these changes and identify any remaining gaps in awareness. We will also work with the student leadership team to help shape safeguarding messages and ensure they are relevant to the risks, responsibilities and experiences faced by older students</t>
+  </si>
+  <si>
+    <t>Do pupils say they feel safe, and can they identify trusted adults to go to? What does pupil voice indicate about how well concerns are listened to and acted upon and their confidence in who to go to if they need support? Is safeguarding, including online safety, embedded in what pupils are taught? How do leaders ensure that pupils off-site are safe and accounted for? Who would pupils speak to if they had a safeguarding concern? Would they say that staff listen to them, and how do they know that? What would happen next for them?</t>
+  </si>
+  <si>
+    <t>Can you see this across the school? Is safeguarding clearly understood as everyone’s responsibility across the school? Can leaders demonstrate strong oversight of safeguarding practice, including how they review and act on concerns? How effective is multi-agency working in securing support for pupils and families (and how effectively is it evidenced and seen in chronology recording that suitable suppotr has been sought at each stage and the needs of children and families championed)? Is there a culture of reveiw and learning lessons to continually improve practice? How do leaders assure themselves that safeguarding systems are working? How are leaders assured of the follow-up on safeguarding concerns? How do leaders spot safeguarding patterns and respond to them?</t>
+  </si>
+  <si>
+    <t>Do staff understand the signs of safeguarding concerns and know how to report them? Does training meet statutory requirements?  Are safeguarding systems used consistently in practice? Can leaders demonstrate that concerns are recorded, followed up and escalated appropriately? How do leaders assure themselves that staff responses are timely and effective? How would staff recognise a safeguarding concern? Do staff know what safeguarding concerns are particularly pertinent to the school? Do all staff know how to record a concern? What follow-up would staff expect?</t>
   </si>
 </sst>
 </file>
@@ -692,13 +692,76 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -710,74 +773,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1133,7 +1133,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="7" customFormat="1" ht="28.5">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="71" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="23"/>
@@ -1148,7 +1148,7 @@
       <c r="I1" s="52"/>
     </row>
     <row r="2" spans="1:9" ht="57">
-      <c r="A2" s="51"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="8" t="s">
         <v>7</v>
       </c>
@@ -1175,438 +1175,438 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="37.5">
-      <c r="A3" s="51"/>
-      <c r="B3" s="48" t="s">
+      <c r="A3" s="72"/>
+      <c r="B3" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="57" t="s">
-        <v>34</v>
+      <c r="C3" s="54" t="s">
+        <v>70</v>
       </c>
       <c r="D3" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="46"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="61" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="37.5">
+      <c r="A4" s="72"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="51"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="62"/>
+    </row>
+    <row r="5" spans="1:9" ht="75">
+      <c r="A5" s="72"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="51"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="62"/>
+    </row>
+    <row r="6" spans="1:9" ht="121.5" customHeight="1">
+      <c r="A6" s="72"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="51"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="63"/>
+    </row>
+    <row r="7" spans="1:9" ht="37.5">
+      <c r="A7" s="72"/>
+      <c r="B7" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="46"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="61" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="37.5">
+      <c r="A8" s="72"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="51"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="62"/>
+    </row>
+    <row r="9" spans="1:9" ht="37.5">
+      <c r="A9" s="72"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="58" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="60"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="69" t="s">
-        <v>68</v>
-      </c>
-      <c r="I3" s="70" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="37.5">
-      <c r="A4" s="51"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="58"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="72"/>
-    </row>
-    <row r="5" spans="1:9" ht="75">
-      <c r="A5" s="51"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="31" t="s">
+      <c r="E9" s="51"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="62"/>
+    </row>
+    <row r="10" spans="1:9" ht="37.5">
+      <c r="A10" s="72"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="58"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="72"/>
-    </row>
-    <row r="6" spans="1:9" ht="121.5" customHeight="1">
-      <c r="A6" s="51"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="58"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="74"/>
-    </row>
-    <row r="7" spans="1:9" ht="37.5">
-      <c r="A7" s="51"/>
-      <c r="B7" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="60"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="69" t="s">
-        <v>70</v>
-      </c>
-      <c r="I7" s="70" t="s">
+      <c r="E10" s="51"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="62"/>
+    </row>
+    <row r="11" spans="1:9" ht="108" customHeight="1">
+      <c r="A11" s="72"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="51"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="63"/>
+    </row>
+    <row r="12" spans="1:9" ht="37.5">
+      <c r="A12" s="72"/>
+      <c r="B12" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="54" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="37.5">
-      <c r="A8" s="51"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="58"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="72"/>
-    </row>
-    <row r="9" spans="1:9" ht="37.5">
-      <c r="A9" s="51"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="58"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="72"/>
-    </row>
-    <row r="10" spans="1:9" ht="37.5">
-      <c r="A10" s="51"/>
-      <c r="B10" s="48"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="58"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="72"/>
-    </row>
-    <row r="11" spans="1:9" ht="108" customHeight="1">
-      <c r="A11" s="51"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="58"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="74"/>
-    </row>
-    <row r="12" spans="1:9" ht="37.5">
-      <c r="A12" s="51"/>
-      <c r="B12" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="57" t="s">
-        <v>36</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="58" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="60"/>
+      <c r="E12" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="46"/>
       <c r="G12" s="30"/>
       <c r="H12" s="20"/>
       <c r="I12" s="20"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="51"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="57"/>
+      <c r="A13" s="72"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="54"/>
       <c r="D13" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" s="58"/>
-      <c r="F13" s="61"/>
+        <v>59</v>
+      </c>
+      <c r="E13" s="51"/>
+      <c r="F13" s="47"/>
       <c r="G13" s="30"/>
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>
     </row>
     <row r="14" spans="1:9" ht="37.5">
-      <c r="A14" s="51"/>
-      <c r="B14" s="48"/>
-      <c r="C14" s="57"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="54"/>
       <c r="D14" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="58"/>
-      <c r="F14" s="61"/>
+        <v>40</v>
+      </c>
+      <c r="E14" s="51"/>
+      <c r="F14" s="47"/>
       <c r="G14" s="30"/>
       <c r="H14" s="20"/>
       <c r="I14" s="20"/>
     </row>
     <row r="15" spans="1:9" ht="37.5">
-      <c r="A15" s="51"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="57"/>
+      <c r="A15" s="72"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="54"/>
       <c r="D15" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" s="58"/>
-      <c r="F15" s="62"/>
+        <v>47</v>
+      </c>
+      <c r="E15" s="51"/>
+      <c r="F15" s="48"/>
       <c r="G15" s="30"/>
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
     </row>
     <row r="16" spans="1:9" ht="37.5">
-      <c r="A16" s="51"/>
-      <c r="B16" s="48" t="s">
+      <c r="A16" s="72"/>
+      <c r="B16" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="57" t="s">
-        <v>37</v>
+      <c r="C16" s="54" t="s">
+        <v>34</v>
       </c>
       <c r="D16" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="60"/>
+      <c r="E16" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="46"/>
       <c r="G16" s="30"/>
       <c r="H16" s="20"/>
       <c r="I16" s="20"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="51"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="57"/>
+      <c r="A17" s="72"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="54"/>
       <c r="D17" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="58"/>
-      <c r="F17" s="61"/>
+        <v>60</v>
+      </c>
+      <c r="E17" s="51"/>
+      <c r="F17" s="47"/>
       <c r="G17" s="30"/>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
     </row>
     <row r="18" spans="1:9" ht="37.5">
-      <c r="A18" s="51"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="57"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="54"/>
       <c r="D18" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" s="58"/>
-      <c r="F18" s="62"/>
+        <v>61</v>
+      </c>
+      <c r="E18" s="51"/>
+      <c r="F18" s="48"/>
       <c r="G18" s="30"/>
       <c r="H18" s="20"/>
       <c r="I18" s="20"/>
     </row>
     <row r="19" spans="1:9" ht="37.5">
-      <c r="A19" s="51"/>
-      <c r="B19" s="48" t="s">
+      <c r="A19" s="72"/>
+      <c r="B19" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="59" t="s">
-        <v>38</v>
+      <c r="C19" s="69" t="s">
+        <v>35</v>
       </c>
       <c r="D19" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="58" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="60"/>
+      <c r="E19" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="46"/>
       <c r="G19" s="30"/>
       <c r="H19" s="20"/>
       <c r="I19" s="20"/>
     </row>
     <row r="20" spans="1:9" ht="37.5">
-      <c r="A20" s="51"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="59"/>
+      <c r="A20" s="72"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="69"/>
       <c r="D20" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="58"/>
-      <c r="F20" s="61"/>
+        <v>62</v>
+      </c>
+      <c r="E20" s="51"/>
+      <c r="F20" s="47"/>
       <c r="G20" s="30"/>
       <c r="H20" s="20"/>
       <c r="I20" s="20"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="51"/>
-      <c r="B21" s="48"/>
-      <c r="C21" s="59"/>
+      <c r="A21" s="72"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="69"/>
       <c r="D21" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="58"/>
-      <c r="F21" s="61"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="47"/>
       <c r="G21" s="30"/>
       <c r="H21" s="20"/>
       <c r="I21" s="20"/>
     </row>
     <row r="22" spans="1:9" ht="37.5">
-      <c r="A22" s="51"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="59"/>
+      <c r="A22" s="72"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="69"/>
       <c r="D22" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="58"/>
-      <c r="F22" s="61"/>
+        <v>41</v>
+      </c>
+      <c r="E22" s="51"/>
+      <c r="F22" s="47"/>
       <c r="G22" s="30"/>
       <c r="H22" s="20"/>
       <c r="I22" s="20"/>
     </row>
     <row r="23" spans="1:9" ht="37.5">
-      <c r="A23" s="51"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="59"/>
+      <c r="A23" s="72"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="69"/>
       <c r="D23" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="E23" s="58"/>
-      <c r="F23" s="62"/>
+        <v>48</v>
+      </c>
+      <c r="E23" s="51"/>
+      <c r="F23" s="48"/>
       <c r="G23" s="30"/>
       <c r="H23" s="20"/>
       <c r="I23" s="20"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="51"/>
-      <c r="B24" s="48" t="s">
+      <c r="A24" s="72"/>
+      <c r="B24" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="59" t="s">
-        <v>39</v>
+      <c r="C24" s="69" t="s">
+        <v>36</v>
       </c>
       <c r="D24" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="58" t="s">
-        <v>57</v>
-      </c>
-      <c r="F24" s="60"/>
+      <c r="E24" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="46"/>
       <c r="G24" s="30"/>
       <c r="H24" s="20"/>
       <c r="I24" s="20"/>
     </row>
     <row r="25" spans="1:9" ht="37.5">
-      <c r="A25" s="51"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="59"/>
+      <c r="A25" s="72"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="69"/>
       <c r="D25" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="58"/>
-      <c r="F25" s="61"/>
+        <v>38</v>
+      </c>
+      <c r="E25" s="51"/>
+      <c r="F25" s="47"/>
       <c r="G25" s="30"/>
       <c r="H25" s="20"/>
       <c r="I25" s="20"/>
     </row>
     <row r="26" spans="1:9" ht="37.5">
-      <c r="A26" s="51"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="59"/>
+      <c r="A26" s="72"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="69"/>
       <c r="D26" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="58"/>
-      <c r="F26" s="62"/>
+        <v>42</v>
+      </c>
+      <c r="E26" s="51"/>
+      <c r="F26" s="48"/>
       <c r="G26" s="30"/>
       <c r="H26" s="20"/>
       <c r="I26" s="20"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="51"/>
-      <c r="B27" s="48" t="s">
+      <c r="A27" s="72"/>
+      <c r="B27" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="59" t="s">
-        <v>42</v>
+      <c r="C27" s="69" t="s">
+        <v>39</v>
       </c>
       <c r="D27" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="58" t="s">
-        <v>58</v>
-      </c>
-      <c r="F27" s="60"/>
+      <c r="E27" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" s="46"/>
       <c r="G27" s="30"/>
       <c r="H27" s="20"/>
       <c r="I27" s="20"/>
     </row>
     <row r="28" spans="1:9" ht="37.5">
-      <c r="A28" s="51"/>
-      <c r="B28" s="48"/>
-      <c r="C28" s="59"/>
+      <c r="A28" s="72"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="69"/>
       <c r="D28" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E28" s="58"/>
-      <c r="F28" s="61"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="47"/>
       <c r="G28" s="30"/>
       <c r="H28" s="20"/>
       <c r="I28" s="20"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="51"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="59"/>
+      <c r="A29" s="72"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="69"/>
       <c r="D29" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E29" s="58"/>
-      <c r="F29" s="61"/>
+        <v>63</v>
+      </c>
+      <c r="E29" s="51"/>
+      <c r="F29" s="47"/>
       <c r="G29" s="30"/>
       <c r="H29" s="20"/>
       <c r="I29" s="20"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="51"/>
-      <c r="B30" s="48"/>
-      <c r="C30" s="59"/>
+      <c r="A30" s="72"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="69"/>
       <c r="D30" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="E30" s="58"/>
-      <c r="F30" s="62"/>
+        <v>64</v>
+      </c>
+      <c r="E30" s="51"/>
+      <c r="F30" s="48"/>
       <c r="G30" s="7"/>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="51"/>
-      <c r="B31" s="48" t="s">
+      <c r="A31" s="72"/>
+      <c r="B31" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="46"/>
+      <c r="C31" s="67"/>
       <c r="D31" s="26"/>
-      <c r="E31" s="53"/>
+      <c r="E31" s="49"/>
       <c r="F31" s="10"/>
       <c r="G31" s="7"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
     </row>
     <row r="32" spans="1:9" s="45" customFormat="1" ht="53.25" customHeight="1">
-      <c r="A32" s="51"/>
-      <c r="B32" s="49"/>
-      <c r="C32" s="47"/>
+      <c r="A32" s="72"/>
+      <c r="B32" s="70"/>
+      <c r="C32" s="68"/>
       <c r="D32" s="24"/>
-      <c r="E32" s="54"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="10"/>
     </row>
     <row r="33" spans="1:7">
@@ -2272,17 +2272,19 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="F19:F23"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="F27:F30"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="E19:E23"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="E27:E30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="A1:A32"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="C19:C23"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="C24:C26"/>
     <mergeCell ref="G1:I1"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="C3:C6"/>
@@ -2298,19 +2300,17 @@
     <mergeCell ref="I7:I11"/>
     <mergeCell ref="H7:H11"/>
     <mergeCell ref="G7:G11"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="A1:A32"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="B19:B23"/>
-    <mergeCell ref="C19:C23"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="E19:E23"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="E27:E30"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="F19:F23"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="F27:F30"/>
   </mergeCells>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2332,18 +2332,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.5">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="74" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="28"/>
-      <c r="D1" s="55" t="s">
+      <c r="D1" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
     </row>
     <row r="2" spans="1:6" ht="28.5">
-      <c r="A2" s="56"/>
+      <c r="A2" s="74"/>
       <c r="B2" s="8" t="s">
         <v>9</v>
       </c>
@@ -2361,7 +2361,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="37.5">
-      <c r="A3" s="56"/>
+      <c r="A3" s="74"/>
       <c r="B3" s="25" t="s">
         <v>25</v>
       </c>
@@ -2371,7 +2371,7 @@
       <c r="F3" s="27"/>
     </row>
     <row r="4" spans="1:6" ht="37.5">
-      <c r="A4" s="56"/>
+      <c r="A4" s="74"/>
       <c r="B4" s="17" t="s">
         <v>26</v>
       </c>
@@ -2381,7 +2381,7 @@
       <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" ht="18.75">
-      <c r="A5" s="56"/>
+      <c r="A5" s="74"/>
       <c r="B5" s="17" t="s">
         <v>27</v>
       </c>
@@ -2391,7 +2391,7 @@
       <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="75">
-      <c r="A6" s="56"/>
+      <c r="A6" s="74"/>
       <c r="B6" s="17" t="s">
         <v>28</v>
       </c>
@@ -2401,7 +2401,7 @@
       <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="75">
-      <c r="A7" s="56"/>
+      <c r="A7" s="74"/>
       <c r="B7" s="25" t="s">
         <v>29</v>
       </c>
@@ -2411,7 +2411,7 @@
       <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="93.75">
-      <c r="A8" s="56"/>
+      <c r="A8" s="74"/>
       <c r="B8" s="17" t="s">
         <v>30</v>
       </c>
@@ -2421,7 +2421,7 @@
       <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="37.5">
-      <c r="A9" s="56"/>
+      <c r="A9" s="74"/>
       <c r="B9" s="17" t="s">
         <v>31</v>
       </c>
@@ -2431,7 +2431,7 @@
       <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6" ht="37.5">
-      <c r="A10" s="56"/>
+      <c r="A10" s="74"/>
       <c r="B10" s="17" t="s">
         <v>32</v>
       </c>
@@ -2441,7 +2441,7 @@
       <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" ht="37.5">
-      <c r="A11" s="56"/>
+      <c r="A11" s="74"/>
       <c r="B11" s="17" t="s">
         <v>33</v>
       </c>
@@ -2549,12 +2549,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="5fdd7bd5-dfe2-43de-9945-2e9b9de5cc92" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c8a1ba6e-c165-4125-9273-8620b59b059e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2770,22 +2774,28 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="5fdd7bd5-dfe2-43de-9945-2e9b9de5cc92" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c8a1ba6e-c165-4125-9273-8620b59b059e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C47AF3FC-47B2-49FD-8A72-F48BC58E8BCF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0408C648-02CD-4AD6-91D1-232EB8E7FA3F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="5fdd7bd5-dfe2-43de-9945-2e9b9de5cc92"/>
+    <ds:schemaRef ds:uri="c8a1ba6e-c165-4125-9273-8620b59b059e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2811,19 +2821,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0408C648-02CD-4AD6-91D1-232EB8E7FA3F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C47AF3FC-47B2-49FD-8A72-F48BC58E8BCF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="5fdd7bd5-dfe2-43de-9945-2e9b9de5cc92"/>
-    <ds:schemaRef ds:uri="c8a1ba6e-c165-4125-9273-8620b59b059e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>